--- a/.xlsx files/Production Statistics.xlsx
+++ b/.xlsx files/Production Statistics.xlsx
@@ -495,7 +495,7 @@
     <t>Andasudare</t>
   </si>
   <si>
-    <t>lasri</t>
+    <t>Lasri</t>
   </si>
   <si>
     <t>Deschon</t>
